--- a/public/content-import-templates/01_subjects_template.xlsx
+++ b/public/content-import-templates/01_subjects_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
   <si>
     <t>01 — نموذج المواد الدراسية</t>
   </si>
@@ -41,7 +41,7 @@
     <t>name *</t>
   </si>
   <si>
-    <t>مثال: الفيزياء</t>
+    <t>ملاحظة: مادة عادية: «الفيزياء» — مادة مقسّمة: «المادة الكبرى - القسم» — مثال: التربية الإسلامية - السيرة النبوية</t>
   </si>
   <si>
     <t>grade_slug *</t>
@@ -116,6 +116,18 @@
     <t>ابدأ بتحديد grade_slug و track_code قبل تعبئة المواد.</t>
   </si>
   <si>
+    <t>تقسيم المواد: الاسم بصيغة «اسم المادة الكبرى - اسم القسم الفرعي» والفاصل مسافة + شرطة + مسافة (" - ") حرفياً.</t>
+  </si>
+  <si>
+    <t>المعتمد دائماً «التربية الإسلامية - ...» — لا تستخدم «الإسلامية - ...».</t>
+  </si>
+  <si>
+    <t>وحّد هجاء اسم المادة الكبرى عبر كل أقسامها وإلا ظهرت كمواد منفصلة للطالب.</t>
+  </si>
+  <si>
+    <t>القيم المعتمدة للصف الأول: docs/SUBJECT-GROUPING-GRADE-10-YEMEN-CONTENT-GUIDE.md</t>
+  </si>
+  <si>
     <t>phys-g10-aden</t>
   </si>
   <si>
@@ -138,6 +150,18 @@
   </si>
   <si>
     <t>مسودة</t>
+  </si>
+  <si>
+    <t>islam-g10-sira</t>
+  </si>
+  <si>
+    <t>التربية الإسلامية - السيرة النبوية</t>
+  </si>
+  <si>
+    <t>BookOpen</t>
+  </si>
+  <si>
+    <t>#27ae60</t>
   </si>
 </sst>
 </file>
@@ -535,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -701,6 +725,38 @@
         <v>33</v>
       </c>
     </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -709,7 +765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -752,34 +808,66 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H2">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/public/content-import-templates/01_subjects_template.xlsx
+++ b/public/content-import-templates/01_subjects_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
   <si>
     <t>01 — نموذج المواد الدراسية</t>
   </si>
@@ -35,13 +35,25 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: كود فريد للمادة — مثال: phys-g10-aden</t>
+    <t>ملاحظة: كود فريد للمادة — يُحدَّد مرة واحدة ولا يتغير — مثال: phys-g10-aden</t>
   </si>
   <si>
     <t>name *</t>
   </si>
   <si>
-    <t>ملاحظة: مادة عادية: «الفيزياء» — مادة مقسّمة: «المادة الكبرى - القسم» — مثال: التربية الإسلامية - السيرة النبوية</t>
+    <t>ملاحظة: اسم المادة كما يظهر للطالب — مثال: اللغة العربية - النحو</t>
+  </si>
+  <si>
+    <t>group_code</t>
+  </si>
+  <si>
+    <t>ملاحظة: اختياري — لتجميع أقسام مادة واحدة (SUBJECT_AS_BRANCH) — مثال: arabic-g10-aden</t>
+  </si>
+  <si>
+    <t>group_name</t>
+  </si>
+  <si>
+    <t>ملاحظة: اسم المجموعة المعروض — موحّد لكل الأقسام — مثال: اللغة العربية</t>
   </si>
   <si>
     <t>grade_slug *</t>
@@ -116,16 +128,19 @@
     <t>ابدأ بتحديد grade_slug و track_code قبل تعبئة المواد.</t>
   </si>
   <si>
-    <t>تقسيم المواد: الاسم بصيغة «اسم المادة الكبرى - اسم القسم الفرعي» والفاصل مسافة + شرطة + مسافة (" - ") حرفياً.</t>
-  </si>
-  <si>
-    <t>المعتمد دائماً «التربية الإسلامية - ...» — لا تستخدم «الإسلامية - ...».</t>
-  </si>
-  <si>
-    <t>وحّد هجاء اسم المادة الكبرى عبر كل أقسامها وإلا ظهرت كمواد منفصلة للطالب.</t>
-  </si>
-  <si>
-    <t>القيم المعتمدة للصف الأول: docs/SUBJECT-GROUPING-GRADE-10-YEMEN-CONTENT-GUIDE.md</t>
+    <t>subject_code يُحدَّد مرة واحدة عند الإنشاء ولا يمكن تغييره لاحقاً.</t>
+  </si>
+  <si>
+    <t>المادة المتفرعة: كل قسم مادة مستقلة بكود خاص، ويُجمَّعون بنفس group_code و group_name.</t>
+  </si>
+  <si>
+    <t>group_code يُترك فارغاً للمواد غير المتفرعة، وبعد تعيينه لا يمكن تغييره.</t>
+  </si>
+  <si>
+    <t>group_name يجب أن يكون موحّداً حرفياً لكل الأقسام التي تحمل نفس group_code.</t>
+  </si>
+  <si>
+    <t>group_code للعرض فقط — لا يؤثر على الصلاحيات ولا على استهداف الأسئلة.</t>
   </si>
   <si>
     <t>phys-g10-aden</t>
@@ -134,6 +149,9 @@
     <t>الفيزياء</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>grade-10</t>
   </si>
   <si>
@@ -146,22 +164,31 @@
     <t>#dc2626</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>مسودة</t>
   </si>
   <si>
-    <t>islam-g10-sira</t>
-  </si>
-  <si>
-    <t>التربية الإسلامية - السيرة النبوية</t>
+    <t>arabic-g10-nahw</t>
+  </si>
+  <si>
+    <t>اللغة العربية - النحو</t>
+  </si>
+  <si>
+    <t>arabic-g10-aden</t>
+  </si>
+  <si>
+    <t>اللغة العربية</t>
   </si>
   <si>
     <t>BookOpen</t>
   </si>
   <si>
     <t>#27ae60</t>
+  </si>
+  <si>
+    <t>arabic-g10-balagha</t>
+  </si>
+  <si>
+    <t>اللغة العربية - البلاغة</t>
   </si>
 </sst>
 </file>
@@ -559,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -672,89 +699,113 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="B17" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -765,16 +816,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="2" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -805,73 +856,129 @@
       <c r="J1" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2">
+      <c r="H2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2">
         <v>9</v>
       </c>
-      <c r="I2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>45</v>
       </c>
+      <c r="L3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/public/content-import-templates/01_subjects_template.xlsx
+++ b/public/content-import-templates/01_subjects_template.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="تعليمات" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="المواد" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="مرجع الأكواد" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="المواد" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="108">
   <si>
     <t>01 — نموذج المواد الدراسية</t>
   </si>
@@ -35,7 +36,7 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: كود فريد للمادة — يُحدَّد مرة واحدة ولا يتغير — مثال: phys-g10-aden</t>
+    <t>ملاحظة: كود فريد للمادة — يُحدَّد مرة واحدة ولا يتغير — مثال: sub-g10-aden-001</t>
   </si>
   <si>
     <t>name *</t>
@@ -47,7 +48,7 @@
     <t>group_code</t>
   </si>
   <si>
-    <t>ملاحظة: اختياري — لتجميع أقسام مادة واحدة (SUBJECT_AS_BRANCH) — مثال: arabic-g10-aden</t>
+    <t>ملاحظة: اختياري — لتجميع أقسام مادة واحدة (SUBJECT_AS_BRANCH) — مثال: grp-g10-aden-01</t>
   </si>
   <si>
     <t>group_name</t>
@@ -113,7 +114,10 @@
     <t>هذه النماذج لتجهيز المحتوى قبل الاستيراد — لا تستورد بيانات فعلية من هنا تلقائياً.</t>
   </si>
   <si>
-    <t>استخدم أكواداً نصية ثابتة (snake_case أو kebab-case) — لا تستخدم UUID.</t>
+    <t>الأكواد يملكها النظام (TCS-1): نزّل القالب الجاهز من «مركز الاستيراد» ولا تكتب كوداً يدوياً.</t>
+  </si>
+  <si>
+    <t>راجع ورقة «مرجع الأكواد» داخل الملف قبل التعبئة — لا تستخدم UUID ولا حروفاً عربية في الأكواد.</t>
   </si>
   <si>
     <t>لا تضع مفاتيح API أو روابط signed أو أسرار في الملفات.</t>
@@ -143,7 +147,157 @@
     <t>group_code للعرض فقط — لا يؤثر على الصلاحيات ولا على استهداف الأسئلة.</t>
   </si>
   <si>
-    <t>phys-g10-aden</t>
+    <t>مرجع الأكواد الرسمي — TCS-1</t>
+  </si>
+  <si>
+    <t>— صيغ الأكواد —</t>
+  </si>
+  <si>
+    <t>مادة</t>
+  </si>
+  <si>
+    <t>sub-{gradeShort}-{trackCode}-{subjectNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: sub-g10-aden-003</t>
+  </si>
+  <si>
+    <t>مجموعة مواد</t>
+  </si>
+  <si>
+    <t>grp-{gradeShort}-{trackCode}-{groupNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: grp-g10-aden-01</t>
+  </si>
+  <si>
+    <t>وحدة</t>
+  </si>
+  <si>
+    <t>unit-{gradeShort}-{trackCode}-{subjectNo:003}-{unitNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: unit-g10-aden-003-02</t>
+  </si>
+  <si>
+    <t>درس</t>
+  </si>
+  <si>
+    <t>lesson-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: lesson-g10-aden-003-004</t>
+  </si>
+  <si>
+    <t>شرح</t>
+  </si>
+  <si>
+    <t>exp-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: exp-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>مورد</t>
+  </si>
+  <si>
+    <t>res-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: res-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>تقييم</t>
+  </si>
+  <si>
+    <t>asm-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: asm-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>سؤال</t>
+  </si>
+  <si>
+    <t>q-{gradeShort}-{trackCode}-{subjectNo:003}-{questionNo:05}</t>
+  </si>
+  <si>
+    <t>مثال: q-g10-aden-003-00007</t>
+  </si>
+  <si>
+    <t>— القواعد —</t>
+  </si>
+  <si>
+    <t>نظام الأكواد الرسمي: TCS-1 — الأكواد يولّدها النظام ولا ينشئها المشغّل يدوياً.</t>
+  </si>
+  <si>
+    <t>الكود مستقل عن الاسم العربي: تغيير الاسم لا يغيّر الكود أبداً.</t>
+  </si>
+  <si>
+    <t>كود الدرس لا يحتوي على كود الوحدة، لذلك يمكن نقل الدرس بين الوحدات دون تغيير هويته.</t>
+  </si>
+  <si>
+    <t>كود السؤال لا يحتوي على الدرس، لأنه هوية ثابتة عبر المراجعات والاستهداف.</t>
+  </si>
+  <si>
+    <t>الصف والمسار داخل الكود مأخوذان من البيانات المرجعية الرسمية فقط.</t>
+  </si>
+  <si>
+    <t>أي كود سبق تخصيصه لا يُعاد استخدامه لكيان آخر حتى بعد الحذف.</t>
+  </si>
+  <si>
+    <t>— الصفوف المعتمدة —</t>
+  </si>
+  <si>
+    <t>g10</t>
+  </si>
+  <si>
+    <t>grade-10</t>
+  </si>
+  <si>
+    <t>الصف الأول الثانوي</t>
+  </si>
+  <si>
+    <t>g11</t>
+  </si>
+  <si>
+    <t>grade-11</t>
+  </si>
+  <si>
+    <t>الصف الثاني الثانوي</t>
+  </si>
+  <si>
+    <t>g12</t>
+  </si>
+  <si>
+    <t>grade-12</t>
+  </si>
+  <si>
+    <t>الصف الثالث الثانوي</t>
+  </si>
+  <si>
+    <t>— المسارات المعتمدة —</t>
+  </si>
+  <si>
+    <t>sanaa</t>
+  </si>
+  <si>
+    <t>منهج صنعاء</t>
+  </si>
+  <si>
+    <t>aden</t>
+  </si>
+  <si>
+    <t>منهج عدن</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>آخر</t>
+  </si>
+  <si>
+    <t>sub-g10-aden-001</t>
   </si>
   <si>
     <t>الفيزياء</t>
@@ -152,12 +306,6 @@
     <t/>
   </si>
   <si>
-    <t>grade-10</t>
-  </si>
-  <si>
-    <t>aden</t>
-  </si>
-  <si>
     <t>⚛️</t>
   </si>
   <si>
@@ -167,13 +315,13 @@
     <t>مسودة</t>
   </si>
   <si>
-    <t>arabic-g10-nahw</t>
+    <t>sub-g10-aden-002</t>
   </si>
   <si>
     <t>اللغة العربية - النحو</t>
   </si>
   <si>
-    <t>arabic-g10-aden</t>
+    <t>grp-g10-aden-01</t>
   </si>
   <si>
     <t>اللغة العربية</t>
@@ -185,7 +333,7 @@
     <t>#27ae60</t>
   </si>
   <si>
-    <t>arabic-g10-balagha</t>
+    <t>sub-g10-aden-003</t>
   </si>
   <si>
     <t>اللغة العربية - البلاغة</t>
@@ -586,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -808,6 +956,14 @@
         <v>42</v>
       </c>
     </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -815,6 +971,249 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -865,116 +1264,116 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="J2">
         <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="I3" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="I4" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/public/content-import-templates/01_subjects_template.xlsx
+++ b/public/content-import-templates/01_subjects_template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
   <si>
     <t>01 — نموذج المواد الدراسية</t>
   </si>
@@ -36,7 +36,7 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: كود فريد للمادة — يُحدَّد مرة واحدة ولا يتغير — مثال: sub-g10-aden-001</t>
+    <t>ملاحظة: كود فريد للمادة يولّده النظام (TCS-2) — لا يتغير ولا يحتوي المسار — مثال: sub-g10-001</t>
   </si>
   <si>
     <t>name *</t>
@@ -48,7 +48,7 @@
     <t>group_code</t>
   </si>
   <si>
-    <t>ملاحظة: اختياري — لتجميع أقسام مادة واحدة (SUBJECT_AS_BRANCH) — مثال: grp-g10-aden-01</t>
+    <t>ملاحظة: اختياري — لتجميع أقسام مادة واحدة (SUBJECT_AS_BRANCH) — مثال: grp-g10-01</t>
   </si>
   <si>
     <t>group_name</t>
@@ -63,10 +63,10 @@
     <t>مثال: grade-10</t>
   </si>
   <si>
-    <t>track_code</t>
-  </si>
-  <si>
-    <t>ملاحظة: sanaa | aden — مثال: aden</t>
+    <t>track_codes *</t>
+  </si>
+  <si>
+    <t>ملاحظة: مسار أو أكثر مفصولة بـ | — المادة المشتركة تُدخل مرة واحدة — مثال: sanaa|aden</t>
   </si>
   <si>
     <t>semester</t>
@@ -129,7 +129,10 @@
     <t>حالة المراجعة (إن وُجدت): مسودة | معتمد | يحتاج تعديل</t>
   </si>
   <si>
-    <t>ابدأ بتحديد grade_slug و track_code قبل تعبئة المواد.</t>
+    <t>ابدأ بتحديد grade_slug ثم track_codes (مسار واحد أو أكثر مفصولة بـ |).</t>
+  </si>
+  <si>
+    <t>المادة المشتركة بين المناهج تُدخل مرة واحدة فقط: sanaa|aden — لا تكرر الصف لكل مسار.</t>
   </si>
   <si>
     <t>subject_code يُحدَّد مرة واحدة عند الإنشاء ولا يمكن تغييره لاحقاً.</t>
@@ -297,7 +300,7 @@
     <t>آخر</t>
   </si>
   <si>
-    <t>sub-g10-aden-001</t>
+    <t>sub-g10-001</t>
   </si>
   <si>
     <t>الفيزياء</t>
@@ -306,6 +309,9 @@
     <t/>
   </si>
   <si>
+    <t>sanaa|aden</t>
+  </si>
+  <si>
     <t>⚛️</t>
   </si>
   <si>
@@ -315,13 +321,13 @@
     <t>مسودة</t>
   </si>
   <si>
-    <t>sub-g10-aden-002</t>
+    <t>sub-g10-002</t>
   </si>
   <si>
     <t>اللغة العربية - النحو</t>
   </si>
   <si>
-    <t>grp-g10-aden-01</t>
+    <t>grp-g10-01</t>
   </si>
   <si>
     <t>اللغة العربية</t>
@@ -333,7 +339,7 @@
     <t>#27ae60</t>
   </si>
   <si>
-    <t>sub-g10-aden-003</t>
+    <t>sub-g10-003</t>
   </si>
   <si>
     <t>اللغة العربية - البلاغة</t>
@@ -734,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -962,6 +968,14 @@
       </c>
       <c r="B31" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -982,105 +996,105 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1088,7 +1102,7 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1096,7 +1110,7 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1104,7 +1118,7 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1112,7 +1126,7 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1120,7 +1134,7 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1128,83 +1142,83 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +1233,9 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="10" width="18" customWidth="1"/>
+    <col min="2" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
   </cols>
@@ -1264,116 +1280,116 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J2">
         <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
